--- a/research/traditional_assets/database/data/israel/israel_heathcare_information_and_technology.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_heathcare_information_and_technology.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.31835</v>
+        <v>-0.672</v>
       </c>
       <c r="G2">
-        <v>-0.2473454091193005</v>
+        <v>-3880.000000000001</v>
       </c>
       <c r="H2">
-        <v>-4.28732042473454</v>
+        <v>-18995</v>
       </c>
       <c r="I2">
-        <v>-4.824964522895529</v>
+        <v>-21559.78057964813</v>
       </c>
       <c r="J2">
-        <v>-4.824964522895529</v>
+        <v>-21559.78057964813</v>
       </c>
       <c r="K2">
-        <v>-34.378</v>
+        <v>-40.74</v>
       </c>
       <c r="L2">
-        <v>-4.294565896314803</v>
+        <v>-20370</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>114.6</v>
+        <v>90.45</v>
       </c>
       <c r="V2">
-        <v>0.2956656346749226</v>
+        <v>1.281887755102041</v>
       </c>
       <c r="W2">
-        <v>-0.1415139987827146</v>
+        <v>-0.2355786344344697</v>
       </c>
       <c r="X2">
-        <v>0.06390815538048504</v>
+        <v>0.1314930395373106</v>
       </c>
       <c r="Y2">
-        <v>-0.2054221541631996</v>
+        <v>-0.3670716739717803</v>
       </c>
       <c r="Z2">
-        <v>1.024678688077608</v>
-      </c>
-      <c r="AA2">
-        <v>7.057452686017299</v>
+        <v>0.000234796900680911</v>
       </c>
       <c r="AB2">
-        <v>0.06350295496977043</v>
-      </c>
-      <c r="AC2">
-        <v>6.99394973104753</v>
+        <v>0.1295109669877245</v>
       </c>
       <c r="AD2">
-        <v>0.218</v>
+        <v>0.06</v>
       </c>
       <c r="AE2">
-        <v>3.259205028893618</v>
+        <v>2.622805796481324</v>
       </c>
       <c r="AF2">
-        <v>3.477205028893618</v>
+        <v>2.682805796481324</v>
       </c>
       <c r="AG2">
-        <v>-111.1227949711064</v>
+        <v>-87.76719420351868</v>
       </c>
       <c r="AH2">
-        <v>0.008891351846080406</v>
+        <v>0.03662893259354367</v>
       </c>
       <c r="AI2">
-        <v>0.02825222613787264</v>
+        <v>0.02664611673520806</v>
       </c>
       <c r="AJ2">
-        <v>-0.4019238944472596</v>
+        <v>5.100610428722381</v>
       </c>
       <c r="AK2">
-        <v>-13.10842365996301</v>
+        <v>-8.577040935702952</v>
       </c>
       <c r="AL2">
-        <v>0.136</v>
+        <v>0.017</v>
       </c>
       <c r="AM2">
-        <v>-1.094</v>
+        <v>-1.637</v>
       </c>
       <c r="AN2">
-        <v>-0.005820783936772402</v>
+        <v>-0.001415929203539823</v>
       </c>
       <c r="AO2">
-        <v>-285.0735294117646</v>
+        <v>-2558.235294117647</v>
       </c>
       <c r="AP2">
-        <v>2.967072385215913</v>
+        <v>2.071202223091887</v>
       </c>
       <c r="AQ2">
-        <v>35.43875685557587</v>
+        <v>26.5668906536347</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Compugen Ltd. (NasdaqGM:CGEN)</t>
+          <t>BioLight Life Sciences Ltd. (TASE:BOLT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,25 +710,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0227</v>
+        <v>-0.672</v>
       </c>
       <c r="G3">
-        <v>0.02499999999999991</v>
+        <v>-1180</v>
       </c>
       <c r="H3">
-        <v>-3.85</v>
+        <v>-1695</v>
       </c>
       <c r="I3">
-        <v>-4.40673012572234</v>
+        <v>-1445</v>
       </c>
       <c r="J3">
-        <v>-4.40673012572234</v>
+        <v>-1445</v>
       </c>
       <c r="K3">
-        <v>-34.1</v>
+        <v>-1.54</v>
       </c>
       <c r="L3">
-        <v>-4.2625</v>
+        <v>-770</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,70 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>102.2</v>
+        <v>2.25</v>
       </c>
       <c r="V3">
-        <v>0.2756946317777179</v>
+        <v>0.2628504672897196</v>
       </c>
       <c r="W3">
-        <v>-0.2680817610062893</v>
+        <v>-0.07439613526570049</v>
       </c>
       <c r="X3">
-        <v>0.06383161226303442</v>
+        <v>0.1302569769627809</v>
       </c>
       <c r="Y3">
-        <v>-0.3319133732693237</v>
+        <v>-0.2046531122284814</v>
       </c>
       <c r="Z3">
-        <v>-3.277620650116995</v>
+        <v>0.000234796900680911</v>
       </c>
       <c r="AA3">
-        <v>14.4435896595602</v>
+        <v>-0.3392815214839165</v>
       </c>
       <c r="AB3">
-        <v>0.06350313663103165</v>
+        <v>0.1296913406898328</v>
       </c>
       <c r="AC3">
-        <v>14.38008652292917</v>
+        <v>-0.4689728621737493</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AE3">
-        <v>3.259205028893618</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>3.259205028893618</v>
+        <v>0.06</v>
       </c>
       <c r="AG3">
-        <v>-98.94079497110638</v>
+        <v>-2.19</v>
       </c>
       <c r="AH3">
-        <v>0.008715402602917071</v>
+        <v>0.006960556844547563</v>
       </c>
       <c r="AI3">
-        <v>0.03193445439802237</v>
+        <v>0.003285870755750274</v>
       </c>
       <c r="AJ3">
-        <v>-0.3640752296158172</v>
+        <v>-0.3437990580847723</v>
       </c>
       <c r="AK3">
-        <v>702.7296088320122</v>
+        <v>-0.136789506558401</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="AM3">
-        <v>-1.23</v>
+        <v>-0.237</v>
       </c>
       <c r="AN3">
-        <v>-0</v>
+        <v>-0.02090592334494773</v>
+      </c>
+      <c r="AO3">
+        <v>-170</v>
       </c>
       <c r="AP3">
-        <v>2.901319423233429</v>
+        <v>0.7630662020905923</v>
       </c>
       <c r="AQ3">
-        <v>28.78048780487805</v>
+        <v>12.19409282700422</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BioLight Life Sciences Ltd. (TASE:BOLT)</t>
+          <t>Compugen Ltd. (NasdaqGM:CGEN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -840,26 +837,8 @@
           <t>Heathcare Information and Technology</t>
         </is>
       </c>
-      <c r="D4">
-        <v>-0.614</v>
-      </c>
-      <c r="G4">
-        <v>-435.9999999999999</v>
-      </c>
-      <c r="H4">
-        <v>-704</v>
-      </c>
-      <c r="I4">
-        <v>-674</v>
-      </c>
-      <c r="J4">
-        <v>-674</v>
-      </c>
       <c r="K4">
-        <v>-0.278</v>
-      </c>
-      <c r="L4">
-        <v>-55.6</v>
+        <v>-39.2</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -883,73 +862,61 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>12.4</v>
+        <v>88.2</v>
       </c>
       <c r="V4">
-        <v>0.7337278106508877</v>
+        <v>1.42258064516129</v>
       </c>
       <c r="W4">
-        <v>-0.01494623655913978</v>
+        <v>-0.3967611336032389</v>
       </c>
       <c r="X4">
-        <v>0.06398469849793566</v>
+        <v>0.1327291021118403</v>
       </c>
       <c r="Y4">
-        <v>-0.07893093505707544</v>
-      </c>
-      <c r="Z4">
-        <v>0.0004876621476640982</v>
-      </c>
-      <c r="AA4">
-        <v>-0.3286842875256022</v>
+        <v>-0.5294902357150792</v>
       </c>
       <c r="AB4">
-        <v>0.06350277330850923</v>
-      </c>
-      <c r="AC4">
-        <v>-0.3921870608341114</v>
+        <v>0.1293305932856161</v>
       </c>
       <c r="AD4">
-        <v>0.218</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>2.622805796481324</v>
       </c>
       <c r="AF4">
-        <v>0.218</v>
+        <v>2.622805796481324</v>
       </c>
       <c r="AG4">
-        <v>-12.182</v>
+        <v>-85.57719420351867</v>
       </c>
       <c r="AH4">
-        <v>0.01273513260894964</v>
+        <v>0.04058638067714686</v>
       </c>
       <c r="AI4">
-        <v>0.01037206204205919</v>
+        <v>0.03182136025504354</v>
       </c>
       <c r="AJ4">
-        <v>-2.582026282323019</v>
+        <v>3.62965980874633</v>
       </c>
       <c r="AK4">
-        <v>-1.413553028544906</v>
+        <v>14.8129336125479</v>
       </c>
       <c r="AL4">
-        <v>0.136</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0.136</v>
+        <v>-1.4</v>
       </c>
       <c r="AN4">
-        <v>-0.06507462686567164</v>
-      </c>
-      <c r="AO4">
-        <v>-24.77941176470588</v>
+        <v>-0</v>
       </c>
       <c r="AP4">
-        <v>3.636417910447761</v>
+        <v>2.166237038438645</v>
       </c>
       <c r="AQ4">
-        <v>-24.77941176470588</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/israel/israel_heathcare_information_and_technology.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_heathcare_information_and_technology.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.672</v>
+        <v>-0.347</v>
       </c>
       <c r="G2">
-        <v>-3880.000000000001</v>
+        <v>-0.7601328903654485</v>
       </c>
       <c r="H2">
-        <v>-18995</v>
+        <v>-5.024584717607974</v>
       </c>
       <c r="I2">
-        <v>-21559.78057964813</v>
+        <v>-4.940375542548123</v>
       </c>
       <c r="J2">
-        <v>-21559.78057964813</v>
+        <v>-4.940375542548123</v>
       </c>
       <c r="K2">
-        <v>-40.74</v>
+        <v>-39.45</v>
       </c>
       <c r="L2">
-        <v>-20370</v>
+        <v>-5.242524916943522</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,67 +630,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>90.45</v>
+        <v>50.13</v>
       </c>
       <c r="V2">
-        <v>1.281887755102041</v>
+        <v>0.2761070720423001</v>
       </c>
       <c r="W2">
-        <v>-0.2355786344344697</v>
+        <v>-0.4148458161979535</v>
       </c>
       <c r="X2">
-        <v>0.1314930395373106</v>
+        <v>0.1054600755464705</v>
       </c>
       <c r="Y2">
-        <v>-0.3670716739717803</v>
+        <v>-0.520305891744424</v>
       </c>
       <c r="Z2">
-        <v>0.000234796900680911</v>
+        <v>0.4742547425474254</v>
       </c>
       <c r="AB2">
-        <v>0.1295109669877245</v>
+        <v>0.1048605321445473</v>
       </c>
       <c r="AD2">
-        <v>0.06</v>
+        <v>0.073</v>
       </c>
       <c r="AE2">
-        <v>2.622805796481324</v>
+        <v>1.826629788373143</v>
       </c>
       <c r="AF2">
-        <v>2.682805796481324</v>
+        <v>1.899629788373143</v>
       </c>
       <c r="AG2">
-        <v>-87.76719420351868</v>
+        <v>-48.23037021162686</v>
       </c>
       <c r="AH2">
-        <v>0.03662893259354367</v>
+        <v>0.01035448392959492</v>
       </c>
       <c r="AI2">
-        <v>0.02664611673520806</v>
+        <v>0.02909097332602918</v>
       </c>
       <c r="AJ2">
-        <v>5.100610428722381</v>
+        <v>-0.3617378244294257</v>
       </c>
       <c r="AK2">
-        <v>-8.577040935702952</v>
+        <v>-3.179403247440705</v>
       </c>
       <c r="AL2">
-        <v>0.017</v>
+        <v>0.359</v>
       </c>
       <c r="AM2">
-        <v>-1.637</v>
+        <v>-2.311</v>
       </c>
       <c r="AN2">
-        <v>-0.001415929203539823</v>
+        <v>-0.002012627167709741</v>
       </c>
       <c r="AO2">
-        <v>-2558.235294117647</v>
+        <v>-104.4846796657382</v>
       </c>
       <c r="AP2">
-        <v>2.071202223091887</v>
+        <v>1.329722649268751</v>
       </c>
       <c r="AQ2">
-        <v>26.5668906536347</v>
+        <v>16.23106880138468</v>
       </c>
     </row>
     <row r="3">
@@ -710,25 +710,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.672</v>
+        <v>-0.535</v>
       </c>
       <c r="G3">
-        <v>-1180</v>
+        <v>-68.8</v>
       </c>
       <c r="H3">
-        <v>-1695</v>
+        <v>-116.4</v>
       </c>
       <c r="I3">
-        <v>-1445</v>
+        <v>-120.4</v>
       </c>
       <c r="J3">
-        <v>-1445</v>
+        <v>-120.4</v>
       </c>
       <c r="K3">
-        <v>-1.54</v>
+        <v>-7.85</v>
       </c>
       <c r="L3">
-        <v>-770</v>
+        <v>-313.9999999999999</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="V3">
-        <v>0.2628504672897196</v>
+        <v>0.3498498498498498</v>
       </c>
       <c r="W3">
-        <v>-0.07439613526570049</v>
+        <v>-0.4337016574585635</v>
       </c>
       <c r="X3">
-        <v>0.1302569769627809</v>
+        <v>0.1054732382151801</v>
       </c>
       <c r="Y3">
-        <v>-0.2046531122284814</v>
+        <v>-0.5391748956737435</v>
       </c>
       <c r="Z3">
-        <v>0.000234796900680911</v>
+        <v>0.00157559715132035</v>
       </c>
       <c r="AA3">
-        <v>-0.3392815214839165</v>
+        <v>-0.1897018970189702</v>
       </c>
       <c r="AB3">
-        <v>0.1296913406898328</v>
+        <v>0.104818382523042</v>
       </c>
       <c r="AC3">
-        <v>-0.4689728621737493</v>
+        <v>-0.2945202795420122</v>
       </c>
       <c r="AD3">
-        <v>0.06</v>
+        <v>0.073</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.06</v>
+        <v>0.073</v>
       </c>
       <c r="AG3">
-        <v>-2.19</v>
+        <v>-2.257</v>
       </c>
       <c r="AH3">
-        <v>0.006960556844547563</v>
+        <v>0.01084212089707411</v>
       </c>
       <c r="AI3">
-        <v>0.003285870755750274</v>
+        <v>0.007106006035238002</v>
       </c>
       <c r="AJ3">
-        <v>-0.3437990580847723</v>
+        <v>-0.5126050420168067</v>
       </c>
       <c r="AK3">
-        <v>-0.136789506558401</v>
+        <v>-0.284149565655294</v>
       </c>
       <c r="AL3">
-        <v>0.017</v>
+        <v>0.359</v>
       </c>
       <c r="AM3">
-        <v>-0.237</v>
+        <v>0.359</v>
       </c>
       <c r="AN3">
-        <v>-0.02090592334494773</v>
+        <v>-0.02457912457912458</v>
       </c>
       <c r="AO3">
-        <v>-170</v>
+        <v>-8.384401114206128</v>
       </c>
       <c r="AP3">
-        <v>0.7630662020905923</v>
+        <v>0.7599326599326599</v>
       </c>
       <c r="AQ3">
-        <v>12.19409282700422</v>
+        <v>-8.384401114206128</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Compugen Ltd. (NasdaqGM:CGEN)</t>
+          <t>Compugen Ltd. (NasdaqCM:CGEN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -837,8 +837,26 @@
           <t>Heathcare Information and Technology</t>
         </is>
       </c>
+      <c r="D4">
+        <v>-0.159</v>
+      </c>
+      <c r="G4">
+        <v>-0.5333333333333333</v>
+      </c>
+      <c r="H4">
+        <v>-4.653333333333333</v>
+      </c>
+      <c r="I4">
+        <v>-4.555510127689951</v>
+      </c>
+      <c r="J4">
+        <v>-4.555510127689951</v>
+      </c>
       <c r="K4">
-        <v>-39.2</v>
+        <v>-31.6</v>
+      </c>
+      <c r="L4">
+        <v>-4.213333333333334</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -862,61 +880,61 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>88.2</v>
+        <v>47.8</v>
       </c>
       <c r="V4">
-        <v>1.42258064516129</v>
+        <v>0.2732990280160091</v>
       </c>
       <c r="W4">
-        <v>-0.3967611336032389</v>
+        <v>-0.3959899749373434</v>
       </c>
       <c r="X4">
-        <v>0.1327291021118403</v>
+        <v>0.1054469128777609</v>
       </c>
       <c r="Y4">
-        <v>-0.5294902357150792</v>
+        <v>-0.5014368878151043</v>
       </c>
       <c r="AB4">
-        <v>0.1293305932856161</v>
+        <v>0.1049026817660526</v>
       </c>
       <c r="AD4">
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>2.622805796481324</v>
+        <v>1.826629788373143</v>
       </c>
       <c r="AF4">
-        <v>2.622805796481324</v>
+        <v>1.826629788373143</v>
       </c>
       <c r="AG4">
-        <v>-85.57719420351867</v>
+        <v>-45.97337021162685</v>
       </c>
       <c r="AH4">
-        <v>0.04058638067714686</v>
+        <v>0.01033590574640901</v>
       </c>
       <c r="AI4">
-        <v>0.03182136025504354</v>
+        <v>0.0331953782268363</v>
       </c>
       <c r="AJ4">
-        <v>3.62965980874633</v>
+        <v>-0.3565855268774955</v>
       </c>
       <c r="AK4">
-        <v>14.8129336125479</v>
+        <v>-6.361661183418156</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1.4</v>
+        <v>-2.67</v>
       </c>
       <c r="AN4">
         <v>-0</v>
       </c>
       <c r="AP4">
-        <v>2.166237038438645</v>
+        <v>1.380540230372266</v>
       </c>
       <c r="AQ4">
-        <v>29</v>
+        <v>12.92134831460674</v>
       </c>
     </row>
   </sheetData>
